--- a/docs/template คำนวณบำนาญ.xlsx
+++ b/docs/template คำนวณบำนาญ.xlsx
@@ -8,19 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hrProject\early-retire\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBD34EB-770F-435D-BECF-EB21641A17C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48074CAD-C7B9-4DB3-92F4-A59039EC900E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ฐานคำนวณ" sheetId="73" r:id="rId1"/>
     <sheet name="retire-non-gfp" sheetId="79" r:id="rId2"/>
-    <sheet name="retire-gfp" sheetId="74" r:id="rId3"/>
+    <sheet name="retire-gfp (3)" sheetId="82" r:id="rId3"/>
+    <sheet name="retire-gfp (2)" sheetId="80" r:id="rId4"/>
+    <sheet name="retire-gfp" sheetId="74" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'retire-gfp'!$A$1:$K$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'retire-gfp'!$A$1:$K$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'retire-gfp (2)'!$A$1:$K$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'retire-gfp (3)'!$A$1:$K$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'retire-non-gfp'!$A$1:$K$42</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'retire-gfp'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'retire-gfp'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'retire-gfp (2)'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'retire-gfp (3)'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'retire-non-gfp'!$16:$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="109">
   <si>
     <t>ฐานในการคำนวณและช่วงเงินเดือนสำหรับการเลื่อนเงินเดือน</t>
   </si>
@@ -366,10 +372,10 @@
   <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="187" formatCode="[$-187041E]d\ mmmm\ yyyy;@"/>
-    <numFmt numFmtId="189" formatCode="[$-D07041E]d\ mmmm\ yyyy;@"/>
-    <numFmt numFmtId="190" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="191" formatCode="#,##0;[Red]#,##0"/>
-    <numFmt numFmtId="197" formatCode="#,##0.00;[Red]#,##0.00"/>
+    <numFmt numFmtId="188" formatCode="[$-D07041E]d\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="189" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="190" formatCode="#,##0;[Red]#,##0"/>
+    <numFmt numFmtId="191" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -877,7 +883,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFill="0"/>
     <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -972,14 +978,14 @@
     <xf numFmtId="187" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="187" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1006,7 +1012,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1045,7 +1051,7 @@
     <xf numFmtId="187" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1054,13 +1060,13 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="187" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1087,10 +1093,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1102,25 +1108,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="187" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1135,18 +1141,18 @@
     <xf numFmtId="43" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="190" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="197" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="190" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1177,7 +1183,7 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1192,7 +1198,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1201,16 +1207,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1226,10 +1232,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1242,10 +1248,10 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="190" fontId="23" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="23" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1254,7 +1260,40 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="190" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1263,9 +1302,21 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1289,54 +1340,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1414,6 +1417,116 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>970915</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>256540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C96ECD26-C5C3-4547-AD3F-649DEA1C2DB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="114300" y="38100"/>
+          <a:ext cx="856615" cy="856615"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>970915</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>256540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8D64F81-A544-434B-A593-2383AC6A8B88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="114300" y="38100"/>
+          <a:ext cx="856615" cy="856615"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1768,14 +1881,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="120"/>
@@ -2341,17 +2454,17 @@
     <row r="1" spans="1:12" s="39" customFormat="1" ht="23.25" customHeight="1">
       <c r="A1" s="44"/>
       <c r="B1" s="44"/>
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
       <c r="L1" s="104" t="s">
         <v>55</v>
       </c>
@@ -2359,15 +2472,15 @@
     <row r="2" spans="1:12" s="39" customFormat="1" ht="27">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
       <c r="L2" s="104" t="s">
         <v>55</v>
       </c>
@@ -2375,15 +2488,15 @@
     <row r="3" spans="1:12" s="39" customFormat="1" ht="27">
       <c r="A3" s="44"/>
       <c r="B3" s="44"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
       <c r="L3" s="104" t="s">
         <v>55</v>
       </c>
@@ -2414,11 +2527,11 @@
         <v>57</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="142">
+      <c r="C5" s="157">
         <v>23839</v>
       </c>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
       <c r="F5" s="9" t="s">
         <v>103</v>
       </c>
@@ -2435,19 +2548,19 @@
         <v>58</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="142">
+      <c r="C6" s="157">
         <v>35464</v>
       </c>
-      <c r="D6" s="142"/>
-      <c r="E6" s="142"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
       <c r="F6" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G6" s="14"/>
-      <c r="H6" s="142">
+      <c r="H6" s="157">
         <v>45931</v>
       </c>
-      <c r="I6" s="142"/>
+      <c r="I6" s="157"/>
       <c r="J6" s="46"/>
       <c r="L6" s="104" t="s">
         <v>55</v>
@@ -2469,11 +2582,11 @@
       </c>
     </row>
     <row r="8" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="143" t="s">
+      <c r="A8" s="158" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
       <c r="D8" s="48"/>
       <c r="E8" s="49" t="s">
         <v>61</v>
@@ -2484,10 +2597,10 @@
       <c r="G8" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="145" t="s">
+      <c r="I8" s="160" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="145"/>
+      <c r="J8" s="160"/>
       <c r="K8" s="105" t="s">
         <v>65</v>
       </c>
@@ -2499,7 +2612,7 @@
       <c r="A9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="149"/>
+      <c r="B9" s="134"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="12">
@@ -2521,7 +2634,7 @@
       <c r="J9" s="16">
         <v>3</v>
       </c>
-      <c r="K9" s="135">
+      <c r="K9" s="146">
         <f>SUM(J9:J14)</f>
         <v>19.400000000000002</v>
       </c>
@@ -2533,7 +2646,7 @@
       <c r="A10" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="150"/>
+      <c r="B10" s="135"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
@@ -2546,7 +2659,7 @@
       <c r="J10" s="16">
         <v>3.3</v>
       </c>
-      <c r="K10" s="136"/>
+      <c r="K10" s="147"/>
       <c r="L10" s="104" t="s">
         <v>55</v>
       </c>
@@ -2555,7 +2668,7 @@
       <c r="A11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="151"/>
+      <c r="B11" s="136"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
       <c r="E11" s="24"/>
@@ -2579,7 +2692,7 @@
       <c r="A12" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="152"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
       <c r="E12" s="28"/>
@@ -2592,7 +2705,7 @@
       <c r="J12" s="16">
         <v>3.2</v>
       </c>
-      <c r="K12" s="146">
+      <c r="K12" s="148">
         <f>ROUND(K9/6,1)</f>
         <v>3.2</v>
       </c>
@@ -2601,11 +2714,11 @@
       </c>
     </row>
     <row r="13" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="151" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="153"/>
-      <c r="C13" s="138"/>
+      <c r="B13" s="152"/>
+      <c r="C13" s="153"/>
       <c r="D13" s="133"/>
       <c r="E13" s="31">
         <f>E9+E11+E12</f>
@@ -2626,24 +2739,24 @@
       <c r="J13" s="16">
         <v>3.3</v>
       </c>
-      <c r="K13" s="147"/>
+      <c r="K13" s="149"/>
       <c r="L13" s="104" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="154" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="139"/>
-      <c r="C14" s="139"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="140">
+      <c r="E14" s="155">
         <f>E13+(F13/12)+(G13/365)</f>
         <v>28.660045662100455</v>
       </c>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
+      <c r="F14" s="155"/>
+      <c r="G14" s="155"/>
       <c r="H14" s="52"/>
       <c r="I14" s="15" t="s">
         <v>101</v>
@@ -2651,7 +2764,7 @@
       <c r="J14" s="16">
         <v>3.3</v>
       </c>
-      <c r="K14" s="148"/>
+      <c r="K14" s="150"/>
       <c r="L14" s="104" t="s">
         <v>55</v>
       </c>
@@ -2734,7 +2847,7 @@
         <f>_xlfn.IFS(C18="","",C18&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>37200</v>
       </c>
-      <c r="F18" s="156">
+      <c r="F18" s="139">
         <v>3.9</v>
       </c>
       <c r="G18" s="66">
@@ -2775,7 +2888,7 @@
         <f>_xlfn.IFS(C19="","",C19&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>49330</v>
       </c>
-      <c r="F19" s="156">
+      <c r="F19" s="139">
         <v>4.2</v>
       </c>
       <c r="G19" s="66">
@@ -2813,7 +2926,7 @@
         <f>_xlfn.IFS(C20="","",C20&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>49330</v>
       </c>
-      <c r="F20" s="157">
+      <c r="F20" s="140">
         <v>3.3</v>
       </c>
       <c r="G20" s="66">
@@ -2851,7 +2964,7 @@
         <f>_xlfn.IFS(C21="","",C21&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>49330</v>
       </c>
-      <c r="F21" s="157">
+      <c r="F21" s="140">
         <v>3.2</v>
       </c>
       <c r="G21" s="66">
@@ -2889,7 +3002,7 @@
         <f>_xlfn.IFS(C22="","",C22&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>49330</v>
       </c>
-      <c r="F22" s="157">
+      <c r="F22" s="140">
         <v>3.3</v>
       </c>
       <c r="G22" s="66">
@@ -2927,7 +3040,7 @@
         <f>_xlfn.IFS(C23="","",C23&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>49330</v>
       </c>
-      <c r="F23" s="156">
+      <c r="F23" s="139">
         <v>3.3</v>
       </c>
       <c r="G23" s="66">
@@ -2965,7 +3078,7 @@
         <f>_xlfn.IFS(C24="","",C24&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>51290</v>
       </c>
-      <c r="F24" s="156">
+      <c r="F24" s="139">
         <v>4</v>
       </c>
       <c r="G24" s="66">
@@ -3003,7 +3116,7 @@
         <f>_xlfn.IFS(C25="","",C25&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>51290</v>
       </c>
-      <c r="F25" s="156">
+      <c r="F25" s="139">
         <v>4.2</v>
       </c>
       <c r="G25" s="66">
@@ -3041,7 +3154,7 @@
         <f>_xlfn.IFS(C26="","",C26&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>51290</v>
       </c>
-      <c r="F26" s="156">
+      <c r="F26" s="139">
         <v>3.2</v>
       </c>
       <c r="G26" s="66">
@@ -3079,7 +3192,7 @@
         <f>_xlfn.IFS(C27="","",C27&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)))</f>
         <v>51290</v>
       </c>
-      <c r="F27" s="156">
+      <c r="F27" s="139">
         <v>3.2</v>
       </c>
       <c r="G27" s="66">
@@ -3099,16 +3212,16 @@
       <c r="M27" s="109"/>
     </row>
     <row r="28" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A28" s="158" t="s">
+      <c r="A28" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="B28" s="159"/>
-      <c r="C28" s="160"/>
-      <c r="D28" s="160"/>
-      <c r="E28" s="160"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="160"/>
-      <c r="H28" s="161"/>
+      <c r="B28" s="142"/>
+      <c r="C28" s="143"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="143"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="144"/>
       <c r="I28" s="73">
         <f>I27</f>
         <v>56840</v>
@@ -3121,7 +3234,7 @@
     </row>
     <row r="29" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
       <c r="A29" s="75"/>
-      <c r="B29" s="155"/>
+      <c r="B29" s="138"/>
       <c r="C29" s="76"/>
       <c r="D29" s="76"/>
       <c r="E29" s="76"/>
@@ -3370,6 +3483,1288 @@
     </row>
     <row r="42" spans="1:12">
       <c r="L42" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:K3"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="E14:G14"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.27500000000000002" right="0.27500000000000002" top="0.39305555555555599" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="66" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;"TH Sarabun New"&amp;14ข้อมูล ณ วันที่ &amp;D</oddFooter>
+  </headerFooter>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="11" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B2B0717-1A75-40E8-BB83-3A72EA5C3BF6}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="2" width="15.875" style="8" customWidth="1"/>
+    <col min="3" max="4" width="10.625" style="40" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="40" customWidth="1"/>
+    <col min="6" max="6" width="9" style="40" customWidth="1"/>
+    <col min="7" max="7" width="12.125" style="40" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="40" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="40" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="40" customWidth="1"/>
+    <col min="11" max="11" width="11.875" style="40" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="40" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A1" s="44"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="156" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="39" customFormat="1" ht="27">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
+      <c r="L2" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="39" customFormat="1" ht="27">
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
+      <c r="L3" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="27">
+      <c r="A4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="I4" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="27">
+      <c r="A5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="157">
+        <v>24473</v>
+      </c>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="132">
+        <f>YEARFRAC(C5,H6)</f>
+        <v>60.416666666666664</v>
+      </c>
+      <c r="L5" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="27">
+      <c r="A6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="157">
+        <v>33604</v>
+      </c>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="157">
+        <v>46539</v>
+      </c>
+      <c r="I6" s="157"/>
+      <c r="J6" s="46"/>
+      <c r="L6" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="39" customFormat="1" ht="9" customHeight="1">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="L7" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="160" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="160"/>
+      <c r="K8" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="134"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12">
+        <f>DATEDIF(C6,H6,"Y")</f>
+        <v>35</v>
+      </c>
+      <c r="F9" s="12">
+        <f>DATEDIF(C6,H6,"YM")</f>
+        <v>5</v>
+      </c>
+      <c r="G9" s="13">
+        <f>DATEDIF(C6,H6,"MD")</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="52"/>
+      <c r="I9" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="54">
+        <v>3.8</v>
+      </c>
+      <c r="K9" s="146">
+        <f>SUM(J9:J14)</f>
+        <v>21.05</v>
+      </c>
+      <c r="L9" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="135"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="54">
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="147"/>
+      <c r="L10" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="136"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="54">
+        <v>2.75</v>
+      </c>
+      <c r="K11" s="106" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="54">
+        <v>4</v>
+      </c>
+      <c r="K12" s="148">
+        <f>ROUND(K9/6,1)</f>
+        <v>3.5</v>
+      </c>
+      <c r="L12" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="151" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="152"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="31">
+        <f>E9+E11+E12</f>
+        <v>35</v>
+      </c>
+      <c r="F13" s="31">
+        <f>F9+F11+F12</f>
+        <v>5</v>
+      </c>
+      <c r="G13" s="32">
+        <f>G9+G11+G12</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="52"/>
+      <c r="I13" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="54">
+        <v>3.7</v>
+      </c>
+      <c r="K13" s="149"/>
+      <c r="L13" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="154" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="155">
+        <f>E13+(F13/12)+(G13/365)</f>
+        <v>35.416666666666664</v>
+      </c>
+      <c r="F14" s="155"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="54">
+        <v>3.5</v>
+      </c>
+      <c r="K14" s="150"/>
+      <c r="L14" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="9.75" customHeight="1">
+      <c r="L15" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="41" customFormat="1" ht="39" customHeight="1">
+      <c r="A16" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="107" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="109"/>
+    </row>
+    <row r="18" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A18" s="63">
+        <v>44713</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="62">
+        <v>35000</v>
+      </c>
+      <c r="D18" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E18" s="64">
+        <f>_xlfn.IFS(C18="","",C18&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>37200</v>
+      </c>
+      <c r="F18" s="65">
+        <v>3.8</v>
+      </c>
+      <c r="G18" s="66">
+        <f>ROUND(E18*F18%,2)</f>
+        <v>1413.6</v>
+      </c>
+      <c r="H18" s="62">
+        <f>IF(C18+ROUNDUP(G18,-1)&gt;=D18,D18-C18,ROUNDUP(G18,-1))</f>
+        <v>1420</v>
+      </c>
+      <c r="I18" s="62">
+        <f t="shared" ref="I18:I29" si="0">C18+H18</f>
+        <v>36420</v>
+      </c>
+      <c r="J18" s="62">
+        <v>4</v>
+      </c>
+      <c r="K18" s="108">
+        <f t="shared" ref="K18:K29" si="1">I18*J18</f>
+        <v>145680</v>
+      </c>
+      <c r="L18" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="109"/>
+    </row>
+    <row r="19" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A19" s="67">
+        <v>44835</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="62">
+        <f>I18</f>
+        <v>36420</v>
+      </c>
+      <c r="D19" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E19" s="64">
+        <f>_xlfn.IFS(C19="","",C19&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>37200</v>
+      </c>
+      <c r="F19" s="65">
+        <v>4.8</v>
+      </c>
+      <c r="G19" s="66">
+        <f>ROUND(E19*F19%,2)</f>
+        <v>1785.6</v>
+      </c>
+      <c r="H19" s="62">
+        <f>IF(C19+ROUNDUP(G19,-1)&gt;=D19,D19-C19,ROUNDUP(G19,-1))</f>
+        <v>1790</v>
+      </c>
+      <c r="I19" s="62">
+        <f t="shared" ref="I19" si="2">C19+H19</f>
+        <v>38210</v>
+      </c>
+      <c r="J19" s="62">
+        <v>6</v>
+      </c>
+      <c r="K19" s="108">
+        <f t="shared" ref="K19" si="3">I19*J19</f>
+        <v>229260</v>
+      </c>
+      <c r="L19" s="104"/>
+      <c r="M19" s="109"/>
+    </row>
+    <row r="20" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A20" s="67">
+        <v>45017</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="62">
+        <f>I18</f>
+        <v>36420</v>
+      </c>
+      <c r="D20" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E20" s="64">
+        <f>_xlfn.IFS(C20="","",C20&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F20" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G20" s="66">
+        <f t="shared" ref="G20:G29" si="4">ROUND(E20*F20%,2)</f>
+        <v>1831.2</v>
+      </c>
+      <c r="H20" s="62">
+        <f t="shared" ref="H20:H29" si="5">IF(C20+ROUNDUP(G20,-1)&gt;=D20,D20-C20,ROUNDUP(G20,-1))</f>
+        <v>1840</v>
+      </c>
+      <c r="I20" s="62">
+        <f t="shared" si="0"/>
+        <v>38260</v>
+      </c>
+      <c r="J20" s="62">
+        <v>6</v>
+      </c>
+      <c r="K20" s="108">
+        <f t="shared" si="1"/>
+        <v>229560</v>
+      </c>
+      <c r="L20" s="110">
+        <v>6</v>
+      </c>
+      <c r="M20" s="109"/>
+    </row>
+    <row r="21" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A21" s="63">
+        <v>45200</v>
+      </c>
+      <c r="B21" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="62">
+        <f t="shared" ref="C21:C29" si="6">I20</f>
+        <v>38260</v>
+      </c>
+      <c r="D21" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E21" s="64">
+        <f>_xlfn.IFS(C21="","",C21&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F21" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G21" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H21" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I21" s="62">
+        <f t="shared" si="0"/>
+        <v>40100</v>
+      </c>
+      <c r="J21" s="62">
+        <v>6</v>
+      </c>
+      <c r="K21" s="108">
+        <f t="shared" si="1"/>
+        <v>240600</v>
+      </c>
+      <c r="L21" s="110">
+        <v>6</v>
+      </c>
+      <c r="M21" s="111"/>
+    </row>
+    <row r="22" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A22" s="63">
+        <v>45383</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="62">
+        <f t="shared" si="6"/>
+        <v>40100</v>
+      </c>
+      <c r="D22" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E22" s="64">
+        <f>_xlfn.IFS(C22="","",C22&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F22" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G22" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H22" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I22" s="62">
+        <f t="shared" si="0"/>
+        <v>41940</v>
+      </c>
+      <c r="J22" s="62">
+        <v>6</v>
+      </c>
+      <c r="K22" s="108">
+        <f t="shared" si="1"/>
+        <v>251640</v>
+      </c>
+      <c r="L22" s="110">
+        <v>6</v>
+      </c>
+      <c r="M22" s="111"/>
+    </row>
+    <row r="23" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A23" s="68">
+        <v>45566</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="62">
+        <f t="shared" si="6"/>
+        <v>41940</v>
+      </c>
+      <c r="D23" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E23" s="64">
+        <f>_xlfn.IFS(C23="","",C23&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F23" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G23" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H23" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I23" s="62">
+        <f t="shared" si="0"/>
+        <v>43780</v>
+      </c>
+      <c r="J23" s="62">
+        <v>6</v>
+      </c>
+      <c r="K23" s="108">
+        <f t="shared" si="1"/>
+        <v>262680</v>
+      </c>
+      <c r="L23" s="110">
+        <v>6</v>
+      </c>
+      <c r="M23" s="111"/>
+    </row>
+    <row r="24" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A24" s="68">
+        <v>45748</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="62">
+        <f t="shared" si="6"/>
+        <v>43780</v>
+      </c>
+      <c r="D24" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E24" s="64">
+        <f>_xlfn.IFS(C24="","",C24&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F24" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G24" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H24" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I24" s="62">
+        <f t="shared" si="0"/>
+        <v>45620</v>
+      </c>
+      <c r="J24" s="62">
+        <v>6</v>
+      </c>
+      <c r="K24" s="108">
+        <f t="shared" si="1"/>
+        <v>273720</v>
+      </c>
+      <c r="L24" s="110">
+        <v>6</v>
+      </c>
+      <c r="M24" s="111"/>
+    </row>
+    <row r="25" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A25" s="68">
+        <v>45931</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="62">
+        <f t="shared" si="6"/>
+        <v>45620</v>
+      </c>
+      <c r="D25" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E25" s="64">
+        <f>_xlfn.IFS(C25="","",C25&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F25" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G25" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H25" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I25" s="62">
+        <f t="shared" si="0"/>
+        <v>47460</v>
+      </c>
+      <c r="J25" s="62">
+        <v>6</v>
+      </c>
+      <c r="K25" s="108">
+        <f t="shared" si="1"/>
+        <v>284760</v>
+      </c>
+      <c r="L25" s="110">
+        <v>6</v>
+      </c>
+      <c r="M25" s="111"/>
+    </row>
+    <row r="26" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A26" s="63">
+        <v>46113</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="62">
+        <f t="shared" si="6"/>
+        <v>47460</v>
+      </c>
+      <c r="D26" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E26" s="64">
+        <f>_xlfn.IFS(C26="","",C26&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F26" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G26" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H26" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I26" s="62">
+        <f t="shared" si="0"/>
+        <v>49300</v>
+      </c>
+      <c r="J26" s="62">
+        <v>6</v>
+      </c>
+      <c r="K26" s="108">
+        <f t="shared" si="1"/>
+        <v>295800</v>
+      </c>
+      <c r="L26" s="110">
+        <v>6</v>
+      </c>
+      <c r="M26" s="111"/>
+    </row>
+    <row r="27" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A27" s="63">
+        <v>46296</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="62">
+        <f t="shared" si="6"/>
+        <v>49300</v>
+      </c>
+      <c r="D27" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E27" s="64">
+        <f>_xlfn.IFS(C27="","",C27&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F27" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G27" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H27" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I27" s="62">
+        <f t="shared" si="0"/>
+        <v>51140</v>
+      </c>
+      <c r="J27" s="62">
+        <v>6</v>
+      </c>
+      <c r="K27" s="108">
+        <f t="shared" si="1"/>
+        <v>306840</v>
+      </c>
+      <c r="L27" s="110">
+        <v>6</v>
+      </c>
+      <c r="M27" s="111"/>
+    </row>
+    <row r="28" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A28" s="63">
+        <v>46478</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="62">
+        <f t="shared" si="6"/>
+        <v>51140</v>
+      </c>
+      <c r="D28" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E28" s="64">
+        <f>_xlfn.IFS(C28="","",C28&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>52320</v>
+      </c>
+      <c r="F28" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G28" s="66">
+        <f t="shared" si="4"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H28" s="62">
+        <f t="shared" si="5"/>
+        <v>1840</v>
+      </c>
+      <c r="I28" s="62">
+        <f t="shared" si="0"/>
+        <v>52980</v>
+      </c>
+      <c r="J28" s="62">
+        <v>2</v>
+      </c>
+      <c r="K28" s="108">
+        <f t="shared" si="1"/>
+        <v>105960</v>
+      </c>
+      <c r="L28" s="110">
+        <v>6</v>
+      </c>
+      <c r="M28" s="111"/>
+    </row>
+    <row r="29" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A29" s="69">
+        <v>46538</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="62">
+        <f t="shared" si="6"/>
+        <v>52980</v>
+      </c>
+      <c r="D29" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E29" s="64">
+        <f>_xlfn.IFS(C29="","",C29&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F29" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G29" s="66">
+        <f t="shared" si="4"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H29" s="62">
+        <f t="shared" si="5"/>
+        <v>2140</v>
+      </c>
+      <c r="I29" s="62">
+        <f t="shared" si="0"/>
+        <v>55120</v>
+      </c>
+      <c r="J29" s="62"/>
+      <c r="K29" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" s="111"/>
+    </row>
+    <row r="30" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A30" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="137"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="74">
+        <f>SUM(J17:J29)</f>
+        <v>60</v>
+      </c>
+      <c r="K30" s="112">
+        <f>SUM(K17:K29)</f>
+        <v>2626500</v>
+      </c>
+      <c r="L30" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A31" s="75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="138"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="113">
+        <f>K30/J30</f>
+        <v>43775</v>
+      </c>
+      <c r="L31" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A32" s="80"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="114"/>
+      <c r="L32" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="2" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A33" s="85"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="2" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A34" s="86" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A35" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="52"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="91">
+        <f>ROUND(I29*E14,2)</f>
+        <v>1952166.67</v>
+      </c>
+      <c r="J35" s="92"/>
+      <c r="K35" s="115" t="s">
+        <v>89</v>
+      </c>
+      <c r="L35" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A36" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="52"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="115"/>
+      <c r="L36" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A37" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="97">
+        <f>ROUND((K31*E14)/50,2)</f>
+        <v>31007.29</v>
+      </c>
+      <c r="J37" s="95"/>
+      <c r="K37" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L37" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A38" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="94">
+        <f>ROUND(K31*70%,2)</f>
+        <v>30642.5</v>
+      </c>
+      <c r="J38" s="98"/>
+      <c r="K38" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L38" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A39" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="95"/>
+      <c r="K39" s="116"/>
+      <c r="L39" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A40" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="94">
+        <f>ROUND(MIN(I37:I38)*15,2)</f>
+        <v>459637.5</v>
+      </c>
+      <c r="J40" s="99"/>
+      <c r="K40" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L40" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A41" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="101">
+        <f>IF(I40&gt;200000,200000,I40)</f>
+        <v>200000</v>
+      </c>
+      <c r="J41" s="102"/>
+      <c r="K41" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L41" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A42" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="101">
+        <f>IF(I40-I41&gt;200000,200000,I40-I41)</f>
+        <v>200000</v>
+      </c>
+      <c r="J42" s="102"/>
+      <c r="K42" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L42" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A43" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="100"/>
+      <c r="I43" s="101">
+        <f>IF(I40-I41-I42&gt;100000,100000,I40-I41-I42)</f>
+        <v>59637.5</v>
+      </c>
+      <c r="J43" s="99"/>
+      <c r="K43" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L43" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A44" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="52"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="94">
+        <f>SUM(I41+I42+I43)</f>
+        <v>459637.5</v>
+      </c>
+      <c r="J44" s="103"/>
+      <c r="K44" s="118" t="s">
+        <v>89</v>
+      </c>
+      <c r="L44" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="L45" s="104" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3400,12 +4795,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E78395-845F-4027-8F59-E5BA51DD94A6}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DE12D8-C145-414D-913A-F1873A703D45}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24"/>
   <cols>
     <col min="1" max="2" width="15.875" style="8" customWidth="1"/>
@@ -3424,17 +4819,17 @@
     <row r="1" spans="1:12" s="39" customFormat="1" ht="23.25" customHeight="1">
       <c r="A1" s="44"/>
       <c r="B1" s="44"/>
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
       <c r="L1" s="104" t="s">
         <v>55</v>
       </c>
@@ -3442,15 +4837,15 @@
     <row r="2" spans="1:12" s="39" customFormat="1" ht="27">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
       <c r="L2" s="104" t="s">
         <v>55</v>
       </c>
@@ -3458,15 +4853,15 @@
     <row r="3" spans="1:12" s="39" customFormat="1" ht="27">
       <c r="A3" s="44"/>
       <c r="B3" s="44"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
       <c r="L3" s="104" t="s">
         <v>55</v>
       </c>
@@ -3497,11 +4892,11 @@
         <v>57</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="142">
-        <v>27760</v>
-      </c>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
+      <c r="C5" s="157">
+        <v>24473</v>
+      </c>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
       <c r="F5" s="9" t="s">
         <v>103</v>
       </c>
@@ -3518,19 +4913,19 @@
         <v>58</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="142">
-        <v>37987</v>
-      </c>
-      <c r="D6" s="142"/>
-      <c r="E6" s="142"/>
+      <c r="C6" s="157">
+        <v>33604</v>
+      </c>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
       <c r="F6" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G6" s="14"/>
-      <c r="H6" s="142">
-        <v>49949</v>
-      </c>
-      <c r="I6" s="142"/>
+      <c r="H6" s="157">
+        <v>46661</v>
+      </c>
+      <c r="I6" s="157"/>
       <c r="J6" s="46"/>
       <c r="L6" s="104" t="s">
         <v>55</v>
@@ -3552,11 +4947,11 @@
       </c>
     </row>
     <row r="8" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="143" t="s">
+      <c r="A8" s="158" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
       <c r="D8" s="48"/>
       <c r="E8" s="49" t="s">
         <v>61</v>
@@ -3567,10 +4962,10 @@
       <c r="G8" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="145" t="s">
+      <c r="I8" s="160" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="145"/>
+      <c r="J8" s="160"/>
       <c r="K8" s="105" t="s">
         <v>65</v>
       </c>
@@ -3582,12 +4977,12 @@
       <c r="A9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="149"/>
+      <c r="B9" s="134"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="12">
         <f>DATEDIF(C6,H6,"Y")</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F9" s="12">
         <f>DATEDIF(C6,H6,"YM")</f>
@@ -3604,7 +4999,7 @@
       <c r="J9" s="54">
         <v>3.8</v>
       </c>
-      <c r="K9" s="135">
+      <c r="K9" s="146">
         <f>SUM(J9:J14)</f>
         <v>21.05</v>
       </c>
@@ -3616,7 +5011,7 @@
       <c r="A10" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="150"/>
+      <c r="B10" s="135"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
@@ -3629,7 +5024,7 @@
       <c r="J10" s="54">
         <v>3.3</v>
       </c>
-      <c r="K10" s="136"/>
+      <c r="K10" s="147"/>
       <c r="L10" s="104" t="s">
         <v>55</v>
       </c>
@@ -3638,7 +5033,7 @@
       <c r="A11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="151"/>
+      <c r="B11" s="136"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
       <c r="E11" s="24"/>
@@ -3662,7 +5057,7 @@
       <c r="A12" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="152"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
       <c r="E12" s="28"/>
@@ -3675,7 +5070,7 @@
       <c r="J12" s="54">
         <v>4</v>
       </c>
-      <c r="K12" s="146">
+      <c r="K12" s="148">
         <f>ROUND(K9/6,1)</f>
         <v>3.5</v>
       </c>
@@ -3684,15 +5079,15 @@
       </c>
     </row>
     <row r="13" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="151" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="153"/>
-      <c r="C13" s="138"/>
+      <c r="B13" s="152"/>
+      <c r="C13" s="153"/>
       <c r="D13" s="133"/>
       <c r="E13" s="31">
         <f>E9+E11+E12</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F13" s="31">
         <f>F9+F11+F12</f>
@@ -3709,24 +5104,24 @@
       <c r="J13" s="54">
         <v>3.7</v>
       </c>
-      <c r="K13" s="147"/>
+      <c r="K13" s="149"/>
       <c r="L13" s="104" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="154" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="139"/>
-      <c r="C14" s="139"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="140">
+      <c r="E14" s="155">
         <f>E13+(F13/12)+(G13/365)</f>
-        <v>32.75</v>
-      </c>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
+        <v>35.75</v>
+      </c>
+      <c r="F14" s="155"/>
+      <c r="G14" s="155"/>
       <c r="H14" s="52"/>
       <c r="I14" s="53" t="s">
         <v>77</v>
@@ -3734,7 +5129,7 @@
       <c r="J14" s="54">
         <v>3.5</v>
       </c>
-      <c r="K14" s="148"/>
+      <c r="K14" s="150"/>
       <c r="L14" s="104" t="s">
         <v>55</v>
       </c>
@@ -3801,13 +5196,13 @@
     </row>
     <row r="18" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
       <c r="A18" s="63">
-        <v>45566</v>
+        <v>44835</v>
       </c>
       <c r="B18" s="63" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="62">
-        <v>49850</v>
+        <v>35000</v>
       </c>
       <c r="D18" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0))</f>
@@ -3815,25 +5210,30 @@
       </c>
       <c r="E18" s="64">
         <f>_xlfn.IFS(C18="","",C18&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>49330</v>
+        <v>37200</v>
       </c>
       <c r="F18" s="65">
         <v>3.8</v>
       </c>
       <c r="G18" s="66">
         <f>ROUND(E18*F18%,2)</f>
-        <v>1874.54</v>
+        <v>1413.6</v>
       </c>
       <c r="H18" s="62">
         <f>IF(C18+ROUNDUP(G18,-1)&gt;=D18,D18-C18,ROUNDUP(G18,-1))</f>
-        <v>1880</v>
+        <v>1420</v>
       </c>
       <c r="I18" s="62">
-        <f t="shared" ref="I18:I42" si="0">C18+H18</f>
-        <v>51730</v>
-      </c>
-      <c r="J18" s="62"/>
-      <c r="K18" s="108"/>
+        <f t="shared" ref="I18:I28" si="0">C18+H18</f>
+        <v>36420</v>
+      </c>
+      <c r="J18" s="62">
+        <v>6</v>
+      </c>
+      <c r="K18" s="108">
+        <f t="shared" ref="K18:K28" si="1">I18*J18</f>
+        <v>218520</v>
+      </c>
       <c r="L18" s="104" t="s">
         <v>55</v>
       </c>
@@ -3841,1321 +5241,2944 @@
     </row>
     <row r="19" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
       <c r="A19" s="67">
-        <v>45748</v>
+        <v>45017</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C19" s="62">
         <f>I18</f>
-        <v>51730</v>
+        <v>36420</v>
       </c>
       <c r="D19" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>69040</v>
+        <v>74320</v>
       </c>
       <c r="E19" s="64">
         <f>_xlfn.IFS(C19="","",C19&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>49330</v>
+        <v>52320</v>
       </c>
       <c r="F19" s="65">
         <v>3.5</v>
       </c>
       <c r="G19" s="66">
-        <f t="shared" ref="G19:G42" si="1">ROUND(E19*F19%,2)</f>
-        <v>1726.55</v>
+        <f t="shared" ref="G19:G28" si="2">ROUND(E19*F19%,2)</f>
+        <v>1831.2</v>
       </c>
       <c r="H19" s="62">
-        <f t="shared" ref="H19:H42" si="2">IF(C19+ROUNDUP(G19,-1)&gt;=D19,D19-C19,ROUNDUP(G19,-1))</f>
-        <v>1730</v>
+        <f t="shared" ref="H19:H28" si="3">IF(C19+ROUNDUP(G19,-1)&gt;=D19,D19-C19,ROUNDUP(G19,-1))</f>
+        <v>1840</v>
       </c>
       <c r="I19" s="62">
         <f t="shared" si="0"/>
-        <v>53460</v>
-      </c>
-      <c r="J19" s="62"/>
-      <c r="K19" s="108"/>
+        <v>38260</v>
+      </c>
+      <c r="J19" s="62">
+        <v>6</v>
+      </c>
+      <c r="K19" s="108">
+        <f t="shared" si="1"/>
+        <v>229560</v>
+      </c>
+      <c r="L19" s="110">
+        <v>6</v>
+      </c>
       <c r="M19" s="109"/>
     </row>
-    <row r="20" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+    <row r="20" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
       <c r="A20" s="63">
-        <v>45931</v>
-      </c>
-      <c r="B20" s="63" t="s">
-        <v>7</v>
+        <v>45200</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>23</v>
       </c>
       <c r="C20" s="62">
-        <f t="shared" ref="C20:C42" si="3">I19</f>
-        <v>53460</v>
+        <f t="shared" ref="C20:C28" si="4">I19</f>
+        <v>38260</v>
       </c>
       <c r="D20" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>69040</v>
+        <v>74320</v>
       </c>
       <c r="E20" s="64">
         <f>_xlfn.IFS(C20="","",C20&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>49330</v>
+        <v>52320</v>
       </c>
       <c r="F20" s="65">
         <v>3.5</v>
       </c>
       <c r="G20" s="66">
-        <f t="shared" si="1"/>
-        <v>1726.55</v>
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
       </c>
       <c r="H20" s="62">
-        <f t="shared" si="2"/>
-        <v>1730</v>
+        <f t="shared" si="3"/>
+        <v>1840</v>
       </c>
       <c r="I20" s="62">
         <f t="shared" si="0"/>
-        <v>55190</v>
-      </c>
-      <c r="J20" s="62"/>
-      <c r="K20" s="108"/>
-      <c r="M20" s="109"/>
-    </row>
-    <row r="21" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A21" s="67">
-        <v>46113</v>
+        <v>40100</v>
+      </c>
+      <c r="J20" s="62">
+        <v>6</v>
+      </c>
+      <c r="K20" s="108">
+        <f t="shared" si="1"/>
+        <v>240600</v>
+      </c>
+      <c r="L20" s="110">
+        <v>6</v>
+      </c>
+      <c r="M20" s="111"/>
+    </row>
+    <row r="21" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A21" s="63">
+        <v>45383</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" s="62">
-        <f t="shared" si="3"/>
-        <v>55190</v>
+        <f t="shared" si="4"/>
+        <v>40100</v>
       </c>
       <c r="D21" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E21" s="64">
         <f>_xlfn.IFS(C21="","",C21&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>52320</v>
       </c>
       <c r="F21" s="65">
         <v>3.5</v>
       </c>
       <c r="G21" s="66">
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H21" s="62">
+        <f t="shared" si="3"/>
+        <v>1840</v>
+      </c>
+      <c r="I21" s="62">
+        <f t="shared" si="0"/>
+        <v>41940</v>
+      </c>
+      <c r="J21" s="62">
+        <v>6</v>
+      </c>
+      <c r="K21" s="108">
         <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H21" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
-      </c>
-      <c r="I21" s="62">
-        <f t="shared" ref="I21:I24" si="4">C21+H21</f>
-        <v>56990</v>
-      </c>
-      <c r="J21" s="62"/>
-      <c r="K21" s="108"/>
-      <c r="M21" s="109"/>
-    </row>
-    <row r="22" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A22" s="63">
-        <v>46296</v>
-      </c>
-      <c r="B22" s="63" t="s">
-        <v>22</v>
+        <v>251640</v>
+      </c>
+      <c r="L21" s="110">
+        <v>6</v>
+      </c>
+      <c r="M21" s="111"/>
+    </row>
+    <row r="22" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A22" s="68">
+        <v>45566</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>23</v>
       </c>
       <c r="C22" s="62">
-        <f t="shared" si="3"/>
-        <v>56990</v>
+        <f t="shared" si="4"/>
+        <v>41940</v>
       </c>
       <c r="D22" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E22" s="64">
         <f>_xlfn.IFS(C22="","",C22&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>52320</v>
       </c>
       <c r="F22" s="65">
         <v>3.5</v>
       </c>
       <c r="G22" s="66">
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H22" s="62">
+        <f t="shared" si="3"/>
+        <v>1840</v>
+      </c>
+      <c r="I22" s="62">
+        <f t="shared" si="0"/>
+        <v>43780</v>
+      </c>
+      <c r="J22" s="62">
+        <v>6</v>
+      </c>
+      <c r="K22" s="108">
         <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H22" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
-      </c>
-      <c r="I22" s="62">
+        <v>262680</v>
+      </c>
+      <c r="L22" s="110">
+        <v>6</v>
+      </c>
+      <c r="M22" s="111"/>
+    </row>
+    <row r="23" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A23" s="68">
+        <v>45748</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="62">
         <f t="shared" si="4"/>
-        <v>58790</v>
-      </c>
-      <c r="J22" s="131"/>
-      <c r="K22" s="130"/>
-      <c r="M22" s="109"/>
-    </row>
-    <row r="23" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A23" s="67">
-        <v>46478</v>
-      </c>
-      <c r="B23" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="62">
-        <f t="shared" si="3"/>
-        <v>58790</v>
+        <v>43780</v>
       </c>
       <c r="D23" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E23" s="64">
         <f>_xlfn.IFS(C23="","",C23&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>52320</v>
       </c>
       <c r="F23" s="65">
         <v>3.5</v>
       </c>
       <c r="G23" s="66">
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H23" s="62">
+        <f t="shared" si="3"/>
+        <v>1840</v>
+      </c>
+      <c r="I23" s="62">
+        <f t="shared" si="0"/>
+        <v>45620</v>
+      </c>
+      <c r="J23" s="62">
+        <v>6</v>
+      </c>
+      <c r="K23" s="108">
         <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H23" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
-      </c>
-      <c r="I23" s="62">
+        <v>273720</v>
+      </c>
+      <c r="L23" s="110">
+        <v>6</v>
+      </c>
+      <c r="M23" s="111"/>
+    </row>
+    <row r="24" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A24" s="68">
+        <v>45931</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="62">
         <f t="shared" si="4"/>
-        <v>60590</v>
-      </c>
-      <c r="J23" s="62"/>
-      <c r="K23" s="130"/>
-      <c r="M23" s="109"/>
-    </row>
-    <row r="24" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A24" s="63">
-        <v>46661</v>
-      </c>
-      <c r="B24" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="62">
-        <f t="shared" si="3"/>
-        <v>60590</v>
+        <v>45620</v>
       </c>
       <c r="D24" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E24" s="64">
         <f>_xlfn.IFS(C24="","",C24&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>52320</v>
       </c>
       <c r="F24" s="65">
         <v>3.5</v>
       </c>
       <c r="G24" s="66">
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
+      </c>
+      <c r="H24" s="62">
+        <f t="shared" si="3"/>
+        <v>1840</v>
+      </c>
+      <c r="I24" s="62">
+        <f t="shared" si="0"/>
+        <v>47460</v>
+      </c>
+      <c r="J24" s="62">
+        <v>6</v>
+      </c>
+      <c r="K24" s="108">
         <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H24" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
-      </c>
-      <c r="I24" s="62">
+        <v>284760</v>
+      </c>
+      <c r="L24" s="110">
+        <v>6</v>
+      </c>
+      <c r="M24" s="111"/>
+    </row>
+    <row r="25" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A25" s="63">
+        <v>46113</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="62">
         <f t="shared" si="4"/>
-        <v>62390</v>
-      </c>
-      <c r="J24" s="62"/>
-      <c r="K24" s="108"/>
-      <c r="M24" s="109"/>
-    </row>
-    <row r="25" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A25" s="67">
-        <v>46844</v>
-      </c>
-      <c r="B25" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="62">
-        <f t="shared" si="3"/>
-        <v>62390</v>
+        <v>47460</v>
       </c>
       <c r="D25" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E25" s="64">
         <f>_xlfn.IFS(C25="","",C25&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>52320</v>
       </c>
       <c r="F25" s="65">
         <v>3.5</v>
       </c>
       <c r="G25" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
       </c>
       <c r="H25" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
+        <f t="shared" si="3"/>
+        <v>1840</v>
       </c>
       <c r="I25" s="62">
         <f t="shared" si="0"/>
-        <v>64190</v>
-      </c>
-      <c r="J25" s="62"/>
-      <c r="K25" s="108"/>
-      <c r="M25" s="109"/>
-    </row>
-    <row r="26" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+        <v>49300</v>
+      </c>
+      <c r="J25" s="62">
+        <v>6</v>
+      </c>
+      <c r="K25" s="108">
+        <f t="shared" si="1"/>
+        <v>295800</v>
+      </c>
+      <c r="L25" s="110">
+        <v>6</v>
+      </c>
+      <c r="M25" s="111"/>
+    </row>
+    <row r="26" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
       <c r="A26" s="63">
-        <v>47027</v>
+        <v>46296</v>
       </c>
       <c r="B26" s="67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="62">
-        <f t="shared" si="3"/>
-        <v>64190</v>
+        <f t="shared" si="4"/>
+        <v>49300</v>
       </c>
       <c r="D26" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E26" s="64">
         <f>_xlfn.IFS(C26="","",C26&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>52320</v>
       </c>
       <c r="F26" s="65">
         <v>3.5</v>
       </c>
       <c r="G26" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
       </c>
       <c r="H26" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
+        <f t="shared" si="3"/>
+        <v>1840</v>
       </c>
       <c r="I26" s="62">
         <f t="shared" si="0"/>
-        <v>65990</v>
-      </c>
-      <c r="J26" s="62"/>
-      <c r="K26" s="108"/>
-      <c r="M26" s="109"/>
-    </row>
-    <row r="27" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A27" s="67">
-        <v>47209</v>
+        <v>51140</v>
+      </c>
+      <c r="J26" s="62">
+        <v>6</v>
+      </c>
+      <c r="K26" s="108">
+        <f t="shared" si="1"/>
+        <v>306840</v>
+      </c>
+      <c r="L26" s="110">
+        <v>6</v>
+      </c>
+      <c r="M26" s="111"/>
+    </row>
+    <row r="27" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A27" s="63">
+        <v>46478</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="62">
-        <f t="shared" si="3"/>
-        <v>65990</v>
+        <f t="shared" si="4"/>
+        <v>51140</v>
       </c>
       <c r="D27" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E27" s="64">
         <f>_xlfn.IFS(C27="","",C27&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>52320</v>
       </c>
       <c r="F27" s="65">
         <v>3.5</v>
       </c>
       <c r="G27" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
+        <f t="shared" si="2"/>
+        <v>1831.2</v>
       </c>
       <c r="H27" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
+        <f t="shared" si="3"/>
+        <v>1840</v>
       </c>
       <c r="I27" s="62">
         <f t="shared" si="0"/>
-        <v>67790</v>
-      </c>
-      <c r="J27" s="62"/>
-      <c r="K27" s="108"/>
-      <c r="M27" s="109"/>
-    </row>
-    <row r="28" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A28" s="63">
-        <v>47392</v>
+        <v>52980</v>
+      </c>
+      <c r="J27" s="62">
+        <v>6</v>
+      </c>
+      <c r="K27" s="108">
+        <f t="shared" si="1"/>
+        <v>317880</v>
+      </c>
+      <c r="L27" s="110">
+        <v>6</v>
+      </c>
+      <c r="M27" s="111"/>
+    </row>
+    <row r="28" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A28" s="69">
+        <v>46660</v>
       </c>
       <c r="B28" s="67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="62">
-        <f t="shared" si="3"/>
-        <v>67790</v>
+        <f t="shared" si="4"/>
+        <v>52980</v>
       </c>
       <c r="D28" s="64">
         <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
+        <v>74320</v>
       </c>
       <c r="E28" s="64">
         <f>_xlfn.IFS(C28="","",C28&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
+        <v>60990</v>
       </c>
       <c r="F28" s="65">
         <v>3.5</v>
       </c>
       <c r="G28" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
+        <f t="shared" si="2"/>
+        <v>2134.65</v>
       </c>
       <c r="H28" s="62">
-        <f t="shared" si="2"/>
-        <v>1800</v>
+        <f t="shared" si="3"/>
+        <v>2140</v>
       </c>
       <c r="I28" s="62">
         <f t="shared" si="0"/>
-        <v>69590</v>
+        <v>55120</v>
       </c>
       <c r="J28" s="62"/>
-      <c r="K28" s="108"/>
-      <c r="M28" s="109"/>
+      <c r="K28" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" s="111"/>
     </row>
     <row r="29" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A29" s="67">
-        <v>47574</v>
-      </c>
-      <c r="B29" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="62">
-        <f t="shared" si="3"/>
-        <v>69590</v>
-      </c>
-      <c r="D29" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
-      </c>
-      <c r="E29" s="64">
-        <f>_xlfn.IFS(C29="","",C29&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
-      </c>
-      <c r="F29" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G29" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H29" s="62">
-        <f t="shared" si="2"/>
-        <v>770</v>
-      </c>
-      <c r="I29" s="62">
-        <f t="shared" si="0"/>
-        <v>70360</v>
-      </c>
-      <c r="J29" s="62"/>
-      <c r="K29" s="108"/>
-      <c r="M29" s="109"/>
+      <c r="A29" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="137"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="74">
+        <f>SUM(J17:J28)</f>
+        <v>60</v>
+      </c>
+      <c r="K29" s="112">
+        <f>SUM(K17:K28)</f>
+        <v>2682000</v>
+      </c>
+      <c r="L29" s="104" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="30" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A30" s="63">
-        <v>47757</v>
-      </c>
-      <c r="B30" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="62">
-        <f t="shared" si="3"/>
-        <v>70360</v>
-      </c>
-      <c r="D30" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
-      </c>
-      <c r="E30" s="64">
-        <f>_xlfn.IFS(C30="","",C30&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
-      </c>
-      <c r="F30" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G30" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H30" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="62">
-        <f t="shared" si="0"/>
-        <v>70360</v>
-      </c>
-      <c r="J30" s="62"/>
-      <c r="K30" s="108"/>
-      <c r="M30" s="109"/>
+      <c r="A30" s="75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="138"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="113">
+        <f>K29/J29</f>
+        <v>44700</v>
+      </c>
+      <c r="L30" s="104" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="31" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A31" s="67">
-        <v>47939</v>
-      </c>
-      <c r="B31" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="62">
-        <f t="shared" si="3"/>
-        <v>70360</v>
-      </c>
-      <c r="D31" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
-      </c>
-      <c r="E31" s="64">
-        <f>_xlfn.IFS(C31="","",C31&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
-      </c>
-      <c r="F31" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G31" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H31" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="62">
-        <f t="shared" si="0"/>
-        <v>70360</v>
-      </c>
-      <c r="J31" s="62"/>
-      <c r="K31" s="108"/>
-      <c r="M31" s="109"/>
-    </row>
-    <row r="32" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A32" s="63">
-        <v>48122</v>
-      </c>
-      <c r="B32" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="62">
-        <f t="shared" si="3"/>
-        <v>70360</v>
-      </c>
-      <c r="D32" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>70360</v>
-      </c>
-      <c r="E32" s="64">
-        <f>_xlfn.IFS(C32="","",C32&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>51290</v>
-      </c>
-      <c r="F32" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G32" s="66">
-        <f t="shared" si="1"/>
-        <v>1795.15</v>
-      </c>
-      <c r="H32" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="62">
-        <f t="shared" si="0"/>
-        <v>70360</v>
-      </c>
-      <c r="J32" s="62">
-        <v>6</v>
-      </c>
-      <c r="K32" s="108">
-        <f t="shared" ref="K32:K42" si="5">I32*J32</f>
-        <v>422160</v>
-      </c>
-      <c r="M32" s="109"/>
-    </row>
-    <row r="33" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A33" s="67">
-        <v>48305</v>
-      </c>
-      <c r="B33" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="62">
-        <f t="shared" si="3"/>
-        <v>70360</v>
-      </c>
-      <c r="D33" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E33" s="64">
-        <f>_xlfn.IFS(C33="","",C33&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F33" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G33" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H33" s="62">
-        <f t="shared" si="2"/>
-        <v>2140</v>
-      </c>
-      <c r="I33" s="62">
-        <f t="shared" si="0"/>
-        <v>72500</v>
-      </c>
-      <c r="J33" s="62">
-        <v>6</v>
-      </c>
-      <c r="K33" s="108">
-        <f t="shared" si="5"/>
-        <v>435000</v>
-      </c>
-      <c r="L33" s="110">
-        <v>6</v>
-      </c>
-      <c r="M33" s="109"/>
-    </row>
-    <row r="34" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A34" s="63">
-        <v>48488</v>
-      </c>
-      <c r="B34" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="62">
-        <f t="shared" si="3"/>
-        <v>72500</v>
-      </c>
-      <c r="D34" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E34" s="64">
-        <f>_xlfn.IFS(C34="","",C34&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F34" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G34" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H34" s="62">
-        <f t="shared" si="2"/>
-        <v>1820</v>
-      </c>
-      <c r="I34" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J34" s="62">
-        <v>6</v>
-      </c>
-      <c r="K34" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L34" s="110">
-        <v>6</v>
-      </c>
-      <c r="M34" s="111"/>
-    </row>
-    <row r="35" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A35" s="63">
-        <v>48670</v>
-      </c>
-      <c r="B35" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D35" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E35" s="64">
-        <f>_xlfn.IFS(C35="","",C35&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F35" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G35" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H35" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J35" s="62">
-        <v>6</v>
-      </c>
-      <c r="K35" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L35" s="110">
-        <v>6</v>
-      </c>
-      <c r="M35" s="111"/>
-    </row>
-    <row r="36" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A36" s="68">
-        <v>48853</v>
-      </c>
-      <c r="B36" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D36" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E36" s="64">
-        <f>_xlfn.IFS(C36="","",C36&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F36" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G36" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H36" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J36" s="62">
-        <v>6</v>
-      </c>
-      <c r="K36" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L36" s="110">
-        <v>6</v>
-      </c>
-      <c r="M36" s="111"/>
-    </row>
-    <row r="37" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A37" s="68">
-        <v>49035</v>
-      </c>
-      <c r="B37" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D37" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E37" s="64">
-        <f>_xlfn.IFS(C37="","",C37&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F37" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G37" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H37" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J37" s="62">
-        <v>6</v>
-      </c>
-      <c r="K37" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L37" s="110">
-        <v>6</v>
-      </c>
-      <c r="M37" s="111"/>
-    </row>
-    <row r="38" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A38" s="68">
-        <v>49218</v>
-      </c>
-      <c r="B38" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D38" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E38" s="64">
-        <f>_xlfn.IFS(C38="","",C38&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F38" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G38" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H38" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J38" s="62">
-        <v>6</v>
-      </c>
-      <c r="K38" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L38" s="110">
-        <v>6</v>
-      </c>
-      <c r="M38" s="111"/>
-    </row>
-    <row r="39" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A39" s="63">
-        <v>49400</v>
-      </c>
-      <c r="B39" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D39" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E39" s="64">
-        <f>_xlfn.IFS(C39="","",C39&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F39" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G39" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H39" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J39" s="62">
-        <v>6</v>
-      </c>
-      <c r="K39" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L39" s="110">
-        <v>6</v>
-      </c>
-      <c r="M39" s="111"/>
-    </row>
-    <row r="40" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A40" s="63">
-        <v>49583</v>
-      </c>
-      <c r="B40" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D40" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E40" s="64">
-        <f>_xlfn.IFS(C40="","",C40&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F40" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G40" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H40" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J40" s="62">
-        <v>6</v>
-      </c>
-      <c r="K40" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L40" s="110">
-        <v>6</v>
-      </c>
-      <c r="M40" s="111"/>
-    </row>
-    <row r="41" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A41" s="63">
-        <v>49766</v>
-      </c>
-      <c r="B41" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D41" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E41" s="64">
-        <f>_xlfn.IFS(C41="","",C41&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F41" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G41" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H41" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J41" s="62">
-        <v>6</v>
-      </c>
-      <c r="K41" s="108">
-        <f t="shared" si="5"/>
-        <v>445920</v>
-      </c>
-      <c r="L41" s="110">
-        <v>6</v>
-      </c>
-      <c r="M41" s="111"/>
-    </row>
-    <row r="42" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
-      <c r="A42" s="69">
-        <v>49948</v>
-      </c>
-      <c r="B42" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="62">
-        <f t="shared" si="3"/>
-        <v>74320</v>
-      </c>
-      <c r="D42" s="64">
-        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0))</f>
-        <v>74320</v>
-      </c>
-      <c r="E42" s="64">
-        <f>_xlfn.IFS(C42="","",C42&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0)))</f>
-        <v>60990</v>
-      </c>
-      <c r="F42" s="65">
-        <v>3.5</v>
-      </c>
-      <c r="G42" s="66">
-        <f t="shared" si="1"/>
-        <v>2134.65</v>
-      </c>
-      <c r="H42" s="62">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="62">
-        <f t="shared" si="0"/>
-        <v>74320</v>
-      </c>
-      <c r="J42" s="62"/>
-      <c r="K42" s="108">
-        <f t="shared" si="5"/>
-        <v>0</v>
+      <c r="A31" s="80"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A32" s="85"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="2" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A33" s="86" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A34" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="52"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91">
+        <f>ROUND(I28*E14,2)</f>
+        <v>1970540</v>
+      </c>
+      <c r="J34" s="92"/>
+      <c r="K34" s="115" t="s">
+        <v>89</v>
+      </c>
+      <c r="L34" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A35" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="52"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="115"/>
+      <c r="L35" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A36" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="97">
+        <f>ROUND((K30*E14)/50,2)</f>
+        <v>31960.5</v>
+      </c>
+      <c r="J36" s="95"/>
+      <c r="K36" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L36" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A37" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="96"/>
+      <c r="I37" s="94">
+        <f>ROUND(K30*70%,2)</f>
+        <v>31290</v>
+      </c>
+      <c r="J37" s="98"/>
+      <c r="K37" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L37" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A38" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="95"/>
+      <c r="I38" s="95"/>
+      <c r="J38" s="95"/>
+      <c r="K38" s="116"/>
+      <c r="L38" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A39" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="94">
+        <f>ROUND(MIN(I36:I37)*15,2)</f>
+        <v>469350</v>
+      </c>
+      <c r="J39" s="99"/>
+      <c r="K39" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L39" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A40" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="101">
+        <f>IF(I39&gt;200000,200000,I39)</f>
+        <v>200000</v>
+      </c>
+      <c r="J40" s="102"/>
+      <c r="K40" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L40" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A41" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="101">
+        <f>IF(I39-I40&gt;200000,200000,I39-I40)</f>
+        <v>200000</v>
+      </c>
+      <c r="J41" s="102"/>
+      <c r="K41" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L41" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A42" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="101">
+        <f>IF(I39-I40-I41&gt;100000,100000,I39-I40-I41)</f>
+        <v>69350</v>
+      </c>
+      <c r="J42" s="99"/>
+      <c r="K42" s="117" t="s">
+        <v>89</v>
       </c>
       <c r="L42" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="M42" s="111"/>
-    </row>
-    <row r="43" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A43" s="70" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" s="154"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="71"/>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74">
-        <f>SUM(J17:J42)</f>
-        <v>60</v>
-      </c>
-      <c r="K43" s="112">
-        <f>SUM(K17:K42)</f>
-        <v>4424520</v>
+    </row>
+    <row r="43" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A43" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="52"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="94">
+        <f>SUM(I40+I41+I42)</f>
+        <v>469350</v>
+      </c>
+      <c r="J43" s="103"/>
+      <c r="K43" s="118" t="s">
+        <v>89</v>
       </c>
       <c r="L43" s="104" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A44" s="75" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" s="155"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="79"/>
-      <c r="K44" s="113">
-        <f>K43/J43</f>
-        <v>73742</v>
-      </c>
+    <row r="44" spans="1:12">
       <c r="L44" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
-      <c r="A45" s="80"/>
-      <c r="B45" s="80"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="82"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="84"/>
-      <c r="K45" s="114"/>
-      <c r="L45" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A46" s="85"/>
-      <c r="B46" s="85"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="37"/>
-      <c r="K46" s="37"/>
-      <c r="L46" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" s="2" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="86" t="s">
-        <v>90</v>
-      </c>
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
-      <c r="D47" s="86"/>
-      <c r="E47" s="86"/>
-      <c r="F47" s="87"/>
-      <c r="G47" s="88"/>
-      <c r="H47" s="89"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="89"/>
-      <c r="K47" s="89"/>
-      <c r="L47" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A48" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="B48" s="52"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="90"/>
-      <c r="I48" s="91">
-        <f>ROUND(I42*E14,2)</f>
-        <v>2433980</v>
-      </c>
-      <c r="J48" s="92"/>
-      <c r="K48" s="115" t="s">
-        <v>89</v>
-      </c>
-      <c r="L48" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A49" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="B49" s="52"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="92"/>
-      <c r="I49" s="92"/>
-      <c r="J49" s="92"/>
-      <c r="K49" s="115"/>
-      <c r="L49" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A50" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="B50" s="40"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="93"/>
-      <c r="I50" s="97">
-        <f>ROUND((K44*E14)/50,2)</f>
-        <v>48301.01</v>
-      </c>
-      <c r="J50" s="95"/>
-      <c r="K50" s="116" t="s">
-        <v>89</v>
-      </c>
-      <c r="L50" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A51" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="96"/>
-      <c r="I51" s="94">
-        <f>ROUND(K44*70%,2)</f>
-        <v>51619.4</v>
-      </c>
-      <c r="J51" s="98"/>
-      <c r="K51" s="116" t="s">
-        <v>89</v>
-      </c>
-      <c r="L51" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="40"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="95"/>
-      <c r="I52" s="95"/>
-      <c r="J52" s="95"/>
-      <c r="K52" s="116"/>
-      <c r="L52" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A53" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="93"/>
-      <c r="I53" s="94">
-        <f>ROUND(MIN(I50:I51)*15,2)</f>
-        <v>724515.15</v>
-      </c>
-      <c r="J53" s="99"/>
-      <c r="K53" s="116" t="s">
-        <v>89</v>
-      </c>
-      <c r="L53" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A54" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="100"/>
-      <c r="I54" s="101">
-        <f>IF(I53&gt;200000,200000,I53)</f>
-        <v>200000</v>
-      </c>
-      <c r="J54" s="102"/>
-      <c r="K54" s="117" t="s">
-        <v>89</v>
-      </c>
-      <c r="L54" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A55" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="100"/>
-      <c r="I55" s="101">
-        <f>IF(I53-I54&gt;200000,200000,I53-I54)</f>
-        <v>200000</v>
-      </c>
-      <c r="J55" s="102"/>
-      <c r="K55" s="117" t="s">
-        <v>89</v>
-      </c>
-      <c r="L55" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A56" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="100"/>
-      <c r="I56" s="101">
-        <f>IF(I53-I54-I55&gt;100000,100000,I53-I54-I55)</f>
-        <v>100000</v>
-      </c>
-      <c r="J56" s="99"/>
-      <c r="K56" s="117" t="s">
-        <v>89</v>
-      </c>
-      <c r="L56" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A57" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="B57" s="52"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="103"/>
-      <c r="I57" s="94">
-        <f>SUM(I54+I55+I56)</f>
-        <v>500000</v>
-      </c>
-      <c r="J57" s="103"/>
-      <c r="K57" s="118" t="s">
-        <v>89</v>
-      </c>
-      <c r="L57" s="104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="L58" s="104" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="E14:G14"/>
     <mergeCell ref="C1:K3"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="I8:J8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.27500000000000002" right="0.27500000000000002" top="0.39305555555555599" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="66" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;"TH Sarabun New"&amp;14ข้อมูล ณ วันที่ &amp;D</oddFooter>
+  </headerFooter>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="11" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E78395-845F-4027-8F59-E5BA51DD94A6}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M68"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="2" width="15.875" style="8" customWidth="1"/>
+    <col min="3" max="4" width="10.625" style="40" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="40" customWidth="1"/>
+    <col min="6" max="6" width="9" style="40" customWidth="1"/>
+    <col min="7" max="7" width="12.125" style="40" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="40" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="40" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="40" customWidth="1"/>
+    <col min="11" max="11" width="11.875" style="40" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="40" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A1" s="44"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="156" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="39" customFormat="1" ht="27">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
+      <c r="L2" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="39" customFormat="1" ht="27">
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
+      <c r="L3" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="27">
+      <c r="A4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="I4" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="27">
+      <c r="A5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="157">
+        <v>29952</v>
+      </c>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="132">
+        <f>YEARFRAC(C5,H6)</f>
+        <v>60.75</v>
+      </c>
+      <c r="L5" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="27">
+      <c r="A6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="157">
+        <v>40909</v>
+      </c>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="157">
+        <v>52140</v>
+      </c>
+      <c r="I6" s="157"/>
+      <c r="J6" s="46"/>
+      <c r="L6" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="39" customFormat="1" ht="9" customHeight="1">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="L7" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="160" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="160"/>
+      <c r="K8" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="134"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12">
+        <f>DATEDIF(C6,H6,"Y")</f>
+        <v>30</v>
+      </c>
+      <c r="F9" s="12">
+        <f>DATEDIF(C6,H6,"YM")</f>
+        <v>9</v>
+      </c>
+      <c r="G9" s="13">
+        <f>DATEDIF(C6,H6,"MD")</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="52"/>
+      <c r="I9" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="54">
+        <v>3.8</v>
+      </c>
+      <c r="K9" s="146">
+        <f>SUM(J9:J14)</f>
+        <v>21.05</v>
+      </c>
+      <c r="L9" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="135"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="54">
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="147"/>
+      <c r="L10" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="136"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="54">
+        <v>2.75</v>
+      </c>
+      <c r="K11" s="106" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="54">
+        <v>4</v>
+      </c>
+      <c r="K12" s="148">
+        <f>ROUND(K9/6,1)</f>
+        <v>3.5</v>
+      </c>
+      <c r="L12" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="151" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="152"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="31">
+        <f>E9+E11+E12</f>
+        <v>30</v>
+      </c>
+      <c r="F13" s="31">
+        <f>F9+F11+F12</f>
+        <v>9</v>
+      </c>
+      <c r="G13" s="32">
+        <f>G9+G11+G12</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="52"/>
+      <c r="I13" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="54">
+        <v>3.7</v>
+      </c>
+      <c r="K13" s="149"/>
+      <c r="L13" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="39" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="154" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="155">
+        <f>E13+(F13/12)+(G13/365)</f>
+        <v>30.75</v>
+      </c>
+      <c r="F14" s="155"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="54">
+        <v>3.5</v>
+      </c>
+      <c r="K14" s="150"/>
+      <c r="L14" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="9.75" customHeight="1">
+      <c r="L15" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="41" customFormat="1" ht="39" customHeight="1">
+      <c r="A16" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="107" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="109"/>
+    </row>
+    <row r="18" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A18" s="63">
+        <v>45931</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="62">
+        <v>35000</v>
+      </c>
+      <c r="D18" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E18" s="64">
+        <f>_xlfn.IFS(C18="","",C18&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B18,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>37200</v>
+      </c>
+      <c r="F18" s="65">
+        <v>3.8</v>
+      </c>
+      <c r="G18" s="66">
+        <f>ROUND(E18*F18%,2)</f>
+        <v>1413.6</v>
+      </c>
+      <c r="H18" s="62">
+        <f>IF(C18+ROUNDUP(G18,-1)&gt;=D18,D18-C18,ROUNDUP(G18,-1))</f>
+        <v>1420</v>
+      </c>
+      <c r="I18" s="62">
+        <f t="shared" ref="I18:I52" si="0">C18+H18</f>
+        <v>36420</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="109"/>
+    </row>
+    <row r="19" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A19" s="67">
+        <v>46113</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="62">
+        <f>I18</f>
+        <v>36420</v>
+      </c>
+      <c r="D19" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E19" s="64">
+        <f>_xlfn.IFS(C19="","",C19&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B19,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>37200</v>
+      </c>
+      <c r="F19" s="65">
+        <v>4.8</v>
+      </c>
+      <c r="G19" s="66">
+        <f t="shared" ref="G19:G28" si="1">ROUND(E19*F19%,2)</f>
+        <v>1785.6</v>
+      </c>
+      <c r="H19" s="62">
+        <f t="shared" ref="H19:H28" si="2">IF(C19+ROUNDUP(G19,-1)&gt;=D19,D19-C19,ROUNDUP(G19,-1))</f>
+        <v>1790</v>
+      </c>
+      <c r="I19" s="62">
+        <f t="shared" ref="I19:I28" si="3">C19+H19</f>
+        <v>38210</v>
+      </c>
+      <c r="J19" s="62"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="109"/>
+    </row>
+    <row r="20" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A20" s="67">
+        <v>46296</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="62">
+        <f t="shared" ref="C20:C52" si="4">I19</f>
+        <v>38210</v>
+      </c>
+      <c r="D20" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E20" s="64">
+        <f>_xlfn.IFS(C20="","",C20&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B20,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>37200</v>
+      </c>
+      <c r="F20" s="65">
+        <v>5.8</v>
+      </c>
+      <c r="G20" s="66">
+        <f t="shared" si="1"/>
+        <v>2157.6</v>
+      </c>
+      <c r="H20" s="62">
+        <f t="shared" si="2"/>
+        <v>2160</v>
+      </c>
+      <c r="I20" s="62">
+        <f t="shared" si="3"/>
+        <v>40370</v>
+      </c>
+      <c r="J20" s="62"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="109"/>
+    </row>
+    <row r="21" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A21" s="67">
+        <v>46478</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="62">
+        <f t="shared" si="4"/>
+        <v>40370</v>
+      </c>
+      <c r="D21" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E21" s="64">
+        <f>_xlfn.IFS(C21="","",C21&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B21,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F21" s="65">
+        <v>6.8</v>
+      </c>
+      <c r="G21" s="66">
+        <f t="shared" si="1"/>
+        <v>3354.44</v>
+      </c>
+      <c r="H21" s="62">
+        <f t="shared" si="2"/>
+        <v>3360</v>
+      </c>
+      <c r="I21" s="62">
+        <f t="shared" si="3"/>
+        <v>43730</v>
+      </c>
+      <c r="J21" s="62"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="109"/>
+    </row>
+    <row r="22" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A22" s="67">
+        <v>46661</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="62">
+        <f t="shared" si="4"/>
+        <v>43730</v>
+      </c>
+      <c r="D22" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E22" s="64">
+        <f>_xlfn.IFS(C22="","",C22&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B22,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F22" s="65">
+        <v>7.8</v>
+      </c>
+      <c r="G22" s="66">
+        <f t="shared" si="1"/>
+        <v>3847.74</v>
+      </c>
+      <c r="H22" s="62">
+        <f t="shared" si="2"/>
+        <v>3850</v>
+      </c>
+      <c r="I22" s="62">
+        <f t="shared" si="3"/>
+        <v>47580</v>
+      </c>
+      <c r="J22" s="62"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="109"/>
+    </row>
+    <row r="23" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A23" s="67">
+        <v>46844</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="62">
+        <f t="shared" si="4"/>
+        <v>47580</v>
+      </c>
+      <c r="D23" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E23" s="64">
+        <f>_xlfn.IFS(C23="","",C23&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B23,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F23" s="65">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G23" s="66">
+        <f t="shared" si="1"/>
+        <v>4341.04</v>
+      </c>
+      <c r="H23" s="62">
+        <f t="shared" si="2"/>
+        <v>4350</v>
+      </c>
+      <c r="I23" s="62">
+        <f t="shared" si="3"/>
+        <v>51930</v>
+      </c>
+      <c r="J23" s="62"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="109"/>
+    </row>
+    <row r="24" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A24" s="67">
+        <v>47027</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="62">
+        <f t="shared" si="4"/>
+        <v>51930</v>
+      </c>
+      <c r="D24" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E24" s="64">
+        <f>_xlfn.IFS(C24="","",C24&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B24,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F24" s="65">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G24" s="66">
+        <f t="shared" si="1"/>
+        <v>4834.34</v>
+      </c>
+      <c r="H24" s="62">
+        <f t="shared" si="2"/>
+        <v>4840</v>
+      </c>
+      <c r="I24" s="62">
+        <f t="shared" si="3"/>
+        <v>56770</v>
+      </c>
+      <c r="J24" s="62"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="109"/>
+    </row>
+    <row r="25" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A25" s="67">
+        <v>47209</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="62">
+        <f t="shared" si="4"/>
+        <v>56770</v>
+      </c>
+      <c r="D25" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E25" s="64">
+        <f>_xlfn.IFS(C25="","",C25&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B25,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F25" s="65">
+        <v>10.8</v>
+      </c>
+      <c r="G25" s="66">
+        <f t="shared" si="1"/>
+        <v>5327.64</v>
+      </c>
+      <c r="H25" s="62">
+        <f t="shared" si="2"/>
+        <v>5330</v>
+      </c>
+      <c r="I25" s="62">
+        <f t="shared" si="3"/>
+        <v>62100</v>
+      </c>
+      <c r="J25" s="62"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="109"/>
+    </row>
+    <row r="26" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A26" s="67">
+        <v>47392</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="62">
+        <f t="shared" si="4"/>
+        <v>62100</v>
+      </c>
+      <c r="D26" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E26" s="64">
+        <f>_xlfn.IFS(C26="","",C26&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B26,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F26" s="65">
+        <v>11.8</v>
+      </c>
+      <c r="G26" s="66">
+        <f t="shared" si="1"/>
+        <v>5820.94</v>
+      </c>
+      <c r="H26" s="62">
+        <f t="shared" si="2"/>
+        <v>5830</v>
+      </c>
+      <c r="I26" s="62">
+        <f t="shared" si="3"/>
+        <v>67930</v>
+      </c>
+      <c r="J26" s="62"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="109"/>
+    </row>
+    <row r="27" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A27" s="67">
+        <v>47574</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="62">
+        <f t="shared" si="4"/>
+        <v>67930</v>
+      </c>
+      <c r="D27" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E27" s="64">
+        <f>_xlfn.IFS(C27="","",C27&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B27,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F27" s="65">
+        <v>12.8</v>
+      </c>
+      <c r="G27" s="66">
+        <f t="shared" si="1"/>
+        <v>6314.24</v>
+      </c>
+      <c r="H27" s="62">
+        <f t="shared" si="2"/>
+        <v>1110</v>
+      </c>
+      <c r="I27" s="62">
+        <f t="shared" si="3"/>
+        <v>69040</v>
+      </c>
+      <c r="J27" s="62"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="109"/>
+    </row>
+    <row r="28" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A28" s="67">
+        <v>47757</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="62">
+        <f t="shared" si="4"/>
+        <v>69040</v>
+      </c>
+      <c r="D28" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E28" s="64">
+        <f>_xlfn.IFS(C28="","",C28&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B28,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F28" s="65">
+        <v>13.8</v>
+      </c>
+      <c r="G28" s="66">
+        <f t="shared" si="1"/>
+        <v>6807.54</v>
+      </c>
+      <c r="H28" s="62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="62">
+        <f t="shared" si="3"/>
+        <v>69040</v>
+      </c>
+      <c r="J28" s="62"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="109"/>
+    </row>
+    <row r="29" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A29" s="67">
+        <v>47939</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="62">
+        <f t="shared" si="4"/>
+        <v>69040</v>
+      </c>
+      <c r="D29" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E29" s="64">
+        <f>_xlfn.IFS(C29="","",C29&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B29,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F29" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G29" s="66">
+        <f t="shared" ref="G29:G52" si="5">ROUND(E29*F29%,2)</f>
+        <v>1726.55</v>
+      </c>
+      <c r="H29" s="62">
+        <f t="shared" ref="H29:H52" si="6">IF(C29+ROUNDUP(G29,-1)&gt;=D29,D29-C29,ROUNDUP(G29,-1))</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="62">
+        <f t="shared" si="0"/>
+        <v>69040</v>
+      </c>
+      <c r="J29" s="62"/>
+      <c r="K29" s="108"/>
+      <c r="M29" s="109"/>
+    </row>
+    <row r="30" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A30" s="63">
+        <v>48122</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="62">
+        <f t="shared" si="4"/>
+        <v>69040</v>
+      </c>
+      <c r="D30" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>69040</v>
+      </c>
+      <c r="E30" s="64">
+        <f>_xlfn.IFS(C30="","",C30&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B30,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>49330</v>
+      </c>
+      <c r="F30" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G30" s="66">
+        <f t="shared" si="5"/>
+        <v>1726.55</v>
+      </c>
+      <c r="H30" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="62">
+        <f t="shared" si="0"/>
+        <v>69040</v>
+      </c>
+      <c r="J30" s="62"/>
+      <c r="K30" s="108"/>
+      <c r="M30" s="109"/>
+    </row>
+    <row r="31" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A31" s="67">
+        <v>48305</v>
+      </c>
+      <c r="B31" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="62">
+        <f t="shared" si="4"/>
+        <v>69040</v>
+      </c>
+      <c r="D31" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E31" s="64">
+        <f>_xlfn.IFS(C31="","",C31&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B31,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F31" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G31" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H31" s="62">
+        <f t="shared" si="6"/>
+        <v>1320</v>
+      </c>
+      <c r="I31" s="62">
+        <f t="shared" ref="I31:I34" si="7">C31+H31</f>
+        <v>70360</v>
+      </c>
+      <c r="J31" s="62"/>
+      <c r="K31" s="108"/>
+      <c r="M31" s="109"/>
+    </row>
+    <row r="32" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A32" s="63">
+        <v>48488</v>
+      </c>
+      <c r="B32" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D32" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E32" s="64">
+        <f>_xlfn.IFS(C32="","",C32&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B32,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F32" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G32" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H32" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="62">
+        <f t="shared" si="7"/>
+        <v>70360</v>
+      </c>
+      <c r="J32" s="131"/>
+      <c r="K32" s="130"/>
+      <c r="M32" s="109"/>
+    </row>
+    <row r="33" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A33" s="67">
+        <v>48670</v>
+      </c>
+      <c r="B33" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D33" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E33" s="64">
+        <f>_xlfn.IFS(C33="","",C33&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B33,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F33" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G33" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H33" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="62">
+        <f t="shared" si="7"/>
+        <v>70360</v>
+      </c>
+      <c r="J33" s="62"/>
+      <c r="K33" s="130"/>
+      <c r="M33" s="109"/>
+    </row>
+    <row r="34" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A34" s="63">
+        <v>48853</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D34" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E34" s="64">
+        <f>_xlfn.IFS(C34="","",C34&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B34,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F34" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G34" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H34" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="62">
+        <f t="shared" si="7"/>
+        <v>70360</v>
+      </c>
+      <c r="J34" s="62"/>
+      <c r="K34" s="108"/>
+      <c r="M34" s="109"/>
+    </row>
+    <row r="35" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A35" s="67">
+        <v>49035</v>
+      </c>
+      <c r="B35" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D35" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E35" s="64">
+        <f>_xlfn.IFS(C35="","",C35&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B35,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F35" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G35" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H35" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J35" s="62"/>
+      <c r="K35" s="108"/>
+      <c r="M35" s="109"/>
+    </row>
+    <row r="36" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A36" s="63">
+        <v>49218</v>
+      </c>
+      <c r="B36" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D36" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E36" s="64">
+        <f>_xlfn.IFS(C36="","",C36&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B36,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F36" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G36" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H36" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J36" s="62"/>
+      <c r="K36" s="108"/>
+      <c r="M36" s="109"/>
+    </row>
+    <row r="37" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A37" s="67">
+        <v>49400</v>
+      </c>
+      <c r="B37" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D37" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E37" s="64">
+        <f>_xlfn.IFS(C37="","",C37&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B37,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F37" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G37" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H37" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J37" s="62"/>
+      <c r="K37" s="108"/>
+      <c r="M37" s="109"/>
+    </row>
+    <row r="38" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A38" s="63">
+        <v>49583</v>
+      </c>
+      <c r="B38" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D38" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E38" s="64">
+        <f>_xlfn.IFS(C38="","",C38&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B38,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F38" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G38" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H38" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J38" s="62"/>
+      <c r="K38" s="108"/>
+      <c r="M38" s="109"/>
+    </row>
+    <row r="39" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A39" s="67">
+        <v>49766</v>
+      </c>
+      <c r="B39" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D39" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E39" s="64">
+        <f>_xlfn.IFS(C39="","",C39&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B39,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F39" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G39" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H39" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J39" s="62"/>
+      <c r="K39" s="108"/>
+      <c r="M39" s="109"/>
+    </row>
+    <row r="40" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A40" s="63">
+        <v>49949</v>
+      </c>
+      <c r="B40" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D40" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E40" s="64">
+        <f>_xlfn.IFS(C40="","",C40&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B40,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F40" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G40" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H40" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J40" s="62"/>
+      <c r="K40" s="108"/>
+      <c r="M40" s="109"/>
+    </row>
+    <row r="41" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A41" s="67">
+        <v>50131</v>
+      </c>
+      <c r="B41" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D41" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E41" s="64">
+        <f>_xlfn.IFS(C41="","",C41&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B41,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F41" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G41" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H41" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J41" s="62"/>
+      <c r="K41" s="108"/>
+      <c r="M41" s="109"/>
+    </row>
+    <row r="42" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A42" s="63">
+        <v>50314</v>
+      </c>
+      <c r="B42" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D42" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>70360</v>
+      </c>
+      <c r="E42" s="64">
+        <f>_xlfn.IFS(C42="","",C42&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B42,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>51290</v>
+      </c>
+      <c r="F42" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G42" s="66">
+        <f t="shared" si="5"/>
+        <v>1795.15</v>
+      </c>
+      <c r="H42" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="62">
+        <f t="shared" si="0"/>
+        <v>70360</v>
+      </c>
+      <c r="J42" s="62">
+        <v>6</v>
+      </c>
+      <c r="K42" s="108">
+        <f t="shared" ref="K42:K52" si="8">I42*J42</f>
+        <v>422160</v>
+      </c>
+      <c r="M42" s="109"/>
+    </row>
+    <row r="43" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A43" s="67">
+        <v>50496</v>
+      </c>
+      <c r="B43" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="62">
+        <f t="shared" si="4"/>
+        <v>70360</v>
+      </c>
+      <c r="D43" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B43,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E43" s="64">
+        <f>_xlfn.IFS(C43="","",C43&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B43,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B43,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B43,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F43" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G43" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H43" s="62">
+        <f t="shared" si="6"/>
+        <v>2140</v>
+      </c>
+      <c r="I43" s="62">
+        <f t="shared" si="0"/>
+        <v>72500</v>
+      </c>
+      <c r="J43" s="62">
+        <v>6</v>
+      </c>
+      <c r="K43" s="108">
+        <f t="shared" si="8"/>
+        <v>435000</v>
+      </c>
+      <c r="L43" s="110">
+        <v>6</v>
+      </c>
+      <c r="M43" s="109"/>
+    </row>
+    <row r="44" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A44" s="63">
+        <v>50679</v>
+      </c>
+      <c r="B44" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="62">
+        <f t="shared" si="4"/>
+        <v>72500</v>
+      </c>
+      <c r="D44" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B44,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E44" s="64">
+        <f>_xlfn.IFS(C44="","",C44&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B44,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B44,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B44,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F44" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G44" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H44" s="62">
+        <f t="shared" si="6"/>
+        <v>1820</v>
+      </c>
+      <c r="I44" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J44" s="62">
+        <v>6</v>
+      </c>
+      <c r="K44" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L44" s="110">
+        <v>6</v>
+      </c>
+      <c r="M44" s="111"/>
+    </row>
+    <row r="45" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A45" s="63">
+        <v>50861</v>
+      </c>
+      <c r="B45" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D45" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B45,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E45" s="64">
+        <f>_xlfn.IFS(C45="","",C45&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B45,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B45,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B45,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F45" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G45" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H45" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J45" s="62">
+        <v>6</v>
+      </c>
+      <c r="K45" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L45" s="110">
+        <v>6</v>
+      </c>
+      <c r="M45" s="111"/>
+    </row>
+    <row r="46" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A46" s="68">
+        <v>51044</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D46" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B46,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E46" s="64">
+        <f>_xlfn.IFS(C46="","",C46&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B46,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B46,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B46,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F46" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G46" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H46" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J46" s="62">
+        <v>6</v>
+      </c>
+      <c r="K46" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L46" s="110">
+        <v>6</v>
+      </c>
+      <c r="M46" s="111"/>
+    </row>
+    <row r="47" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A47" s="68">
+        <v>51227</v>
+      </c>
+      <c r="B47" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D47" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B47,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E47" s="64">
+        <f>_xlfn.IFS(C47="","",C47&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B47,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B47,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B47,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F47" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G47" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H47" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J47" s="62">
+        <v>6</v>
+      </c>
+      <c r="K47" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L47" s="110">
+        <v>6</v>
+      </c>
+      <c r="M47" s="111"/>
+    </row>
+    <row r="48" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A48" s="68">
+        <v>51410</v>
+      </c>
+      <c r="B48" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D48" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B48,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E48" s="64">
+        <f>_xlfn.IFS(C48="","",C48&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B48,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B48,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B48,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F48" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G48" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H48" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J48" s="62">
+        <v>6</v>
+      </c>
+      <c r="K48" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L48" s="110">
+        <v>6</v>
+      </c>
+      <c r="M48" s="111"/>
+    </row>
+    <row r="49" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A49" s="63">
+        <v>51592</v>
+      </c>
+      <c r="B49" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D49" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B49,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E49" s="64">
+        <f>_xlfn.IFS(C49="","",C49&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B49,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B49,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B49,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F49" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G49" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H49" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J49" s="62">
+        <v>6</v>
+      </c>
+      <c r="K49" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L49" s="110">
+        <v>6</v>
+      </c>
+      <c r="M49" s="111"/>
+    </row>
+    <row r="50" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A50" s="63">
+        <v>51775</v>
+      </c>
+      <c r="B50" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D50" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B50,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E50" s="64">
+        <f>_xlfn.IFS(C50="","",C50&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B50,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B50,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B50,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F50" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G50" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H50" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J50" s="62">
+        <v>6</v>
+      </c>
+      <c r="K50" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L50" s="110">
+        <v>6</v>
+      </c>
+      <c r="M50" s="111"/>
+    </row>
+    <row r="51" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A51" s="63">
+        <v>51957</v>
+      </c>
+      <c r="B51" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D51" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B51,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E51" s="64">
+        <f>_xlfn.IFS(C51="","",C51&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B51,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B51,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B51,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F51" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G51" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H51" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J51" s="62">
+        <v>6</v>
+      </c>
+      <c r="K51" s="108">
+        <f t="shared" si="8"/>
+        <v>445920</v>
+      </c>
+      <c r="L51" s="110">
+        <v>6</v>
+      </c>
+      <c r="M51" s="111"/>
+    </row>
+    <row r="52" spans="1:13" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A52" s="69">
+        <v>52139</v>
+      </c>
+      <c r="B52" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="62">
+        <f t="shared" si="4"/>
+        <v>74320</v>
+      </c>
+      <c r="D52" s="64">
+        <f>INDEX(ฐานคำนวณ!$C$5:$C$19,MATCH(B52,ฐานคำนวณ!$B$5:$B$19,0))</f>
+        <v>74320</v>
+      </c>
+      <c r="E52" s="64">
+        <f>_xlfn.IFS(C52="","",C52&gt;INDEX(ฐานคำนวณ!$F$5:$F$19,MATCH(B52,ฐานคำนวณ!$B$5:$B$19,0)),INDEX(ฐานคำนวณ!$D$5:$D$19,MATCH(B52,ฐานคำนวณ!$B$5:$B$19,0)),TRUE,INDEX(ฐานคำนวณ!$E$5:$E$19,MATCH(B52,ฐานคำนวณ!$B$5:$B$19,0)))</f>
+        <v>60990</v>
+      </c>
+      <c r="F52" s="65">
+        <v>3.5</v>
+      </c>
+      <c r="G52" s="66">
+        <f t="shared" si="5"/>
+        <v>2134.65</v>
+      </c>
+      <c r="H52" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="62">
+        <f t="shared" si="0"/>
+        <v>74320</v>
+      </c>
+      <c r="J52" s="62"/>
+      <c r="K52" s="108">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="M52" s="111"/>
+    </row>
+    <row r="53" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A53" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="B53" s="137"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="72"/>
+      <c r="I53" s="73"/>
+      <c r="J53" s="74">
+        <f>SUM(J17:J52)</f>
+        <v>60</v>
+      </c>
+      <c r="K53" s="112">
+        <f>SUM(K17:K52)</f>
+        <v>4424520</v>
+      </c>
+      <c r="L53" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A54" s="75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="138"/>
+      <c r="C54" s="76"/>
+      <c r="D54" s="76"/>
+      <c r="E54" s="76"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="77"/>
+      <c r="I54" s="78"/>
+      <c r="J54" s="79"/>
+      <c r="K54" s="113">
+        <f>K53/J53</f>
+        <v>73742</v>
+      </c>
+      <c r="L54" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="A55" s="80"/>
+      <c r="B55" s="80"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="82"/>
+      <c r="I55" s="83"/>
+      <c r="J55" s="84"/>
+      <c r="K55" s="114"/>
+      <c r="L55" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A56" s="85"/>
+      <c r="B56" s="85"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="37"/>
+      <c r="I56" s="37"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="37"/>
+      <c r="L56" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="2" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A57" s="86" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="86"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="87"/>
+      <c r="G57" s="88"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="89"/>
+      <c r="J57" s="89"/>
+      <c r="K57" s="89"/>
+      <c r="L57" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A58" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="52"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="90"/>
+      <c r="I58" s="91">
+        <f>ROUND(I52*E14,2)</f>
+        <v>2285340</v>
+      </c>
+      <c r="J58" s="92"/>
+      <c r="K58" s="115" t="s">
+        <v>89</v>
+      </c>
+      <c r="L58" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A59" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" s="52"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="92"/>
+      <c r="I59" s="92"/>
+      <c r="J59" s="92"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A60" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60" s="40"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="93"/>
+      <c r="I60" s="97">
+        <f>ROUND((K54*E14)/50,2)</f>
+        <v>45351.33</v>
+      </c>
+      <c r="J60" s="95"/>
+      <c r="K60" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L60" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A61" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="96"/>
+      <c r="I61" s="94">
+        <f>ROUND(K54*70%,2)</f>
+        <v>51619.4</v>
+      </c>
+      <c r="J61" s="98"/>
+      <c r="K61" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L61" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A62" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" s="27"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="95"/>
+      <c r="I62" s="95"/>
+      <c r="J62" s="95"/>
+      <c r="K62" s="116"/>
+      <c r="L62" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A63" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="93"/>
+      <c r="I63" s="94">
+        <f>ROUND(MIN(I60:I61)*15,2)</f>
+        <v>680269.95</v>
+      </c>
+      <c r="J63" s="99"/>
+      <c r="K63" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="L63" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A64" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="100"/>
+      <c r="I64" s="101">
+        <f>IF(I63&gt;200000,200000,I63)</f>
+        <v>200000</v>
+      </c>
+      <c r="J64" s="102"/>
+      <c r="K64" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L64" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A65" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="100"/>
+      <c r="I65" s="101">
+        <f>IF(I63-I64&gt;200000,200000,I63-I64)</f>
+        <v>200000</v>
+      </c>
+      <c r="J65" s="102"/>
+      <c r="K65" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L65" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A66" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="100"/>
+      <c r="I66" s="101">
+        <f>IF(I63-I64-I65&gt;100000,100000,I63-I64-I65)</f>
+        <v>100000</v>
+      </c>
+      <c r="J66" s="99"/>
+      <c r="K66" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="L66" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A67" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B67" s="52"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="40"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="103"/>
+      <c r="I67" s="94">
+        <f>SUM(I64+I65+I66)</f>
+        <v>500000</v>
+      </c>
+      <c r="J67" s="103"/>
+      <c r="K67" s="118" t="s">
+        <v>89</v>
+      </c>
+      <c r="L67" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="L68" s="104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="E14:G14"/>
+    <mergeCell ref="C1:K3"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.27500000000000002" right="0.27500000000000002" top="0.39305555555555599" bottom="0" header="0" footer="0"/>
